--- a/source/8、绩效异常岗位/3、倒包岗/倒包岗-5月.xlsx
+++ b/source/8、绩效异常岗位/3、倒包岗/倒包岗-5月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3378" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3622" uniqueCount="154">
   <si>
     <t>数据日期</t>
   </si>
@@ -485,6 +485,12 @@
   </si>
   <si>
     <t>123.5</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
   </si>
 </sst>
 </file>
@@ -1418,7 +1424,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H734"/>
+  <dimension ref="A1:H786"/>
   <sheetFormatPr defaultColWidth="12.6363636363636" defaultRowHeight="20" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="12.6363636363636" style="1" customWidth="1"/>
@@ -20506,6 +20512,1358 @@
       </c>
       <c r="H734" s="1">
         <v>10.6</v>
+      </c>
+    </row>
+    <row r="735" customHeight="1" spans="1:8">
+      <c r="A735" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B735" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C735" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D735" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E735" s="1">
+        <v>140.2</v>
+      </c>
+      <c r="F735" s="1">
+        <v>58.5</v>
+      </c>
+      <c r="G735" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H735" s="1">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="736" customHeight="1" spans="1:8">
+      <c r="A736" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C736" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D736" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E736" s="1">
+        <v>107.6</v>
+      </c>
+      <c r="F736" s="1">
+        <v>21.6</v>
+      </c>
+      <c r="G736" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H736" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="737" customHeight="1" spans="1:8">
+      <c r="A737" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C737" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D737" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E737" s="1">
+        <v>104.4</v>
+      </c>
+      <c r="F737" s="1">
+        <v>19</v>
+      </c>
+      <c r="G737" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H737" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="738" customHeight="1" spans="1:8">
+      <c r="A738" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B738" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C738" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D738" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E738" s="1">
+        <v>195</v>
+      </c>
+      <c r="F738" s="1">
+        <v>16.7</v>
+      </c>
+      <c r="G738" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H738" s="1">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="739" customHeight="1" spans="1:8">
+      <c r="A739" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B739" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C739" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D739" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E739" s="1">
+        <v>116.5</v>
+      </c>
+      <c r="F739" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="G739" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H739" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="740" customHeight="1" spans="1:8">
+      <c r="A740" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B740" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C740" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D740" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E740" s="1">
+        <v>141.1</v>
+      </c>
+      <c r="F740" s="1">
+        <v>14.7</v>
+      </c>
+      <c r="G740" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H740" s="1">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="741" customHeight="1" spans="1:8">
+      <c r="A741" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B741" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C741" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D741" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E741" s="1">
+        <v>137.7</v>
+      </c>
+      <c r="F741" s="1">
+        <v>13.9</v>
+      </c>
+      <c r="G741" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H741" s="1">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="742" customHeight="1" spans="1:8">
+      <c r="A742" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B742" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C742" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D742" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E742" s="1">
+        <v>83.2</v>
+      </c>
+      <c r="F742" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="G742" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H742" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="743" customHeight="1" spans="1:8">
+      <c r="A743" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B743" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C743" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D743" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E743" s="1">
+        <v>117.3</v>
+      </c>
+      <c r="F743" s="1">
+        <v>13</v>
+      </c>
+      <c r="G743" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H743" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="744" customHeight="1" spans="1:8">
+      <c r="A744" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B744" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C744" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D744" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E744" s="1">
+        <v>145.9</v>
+      </c>
+      <c r="F744" s="1">
+        <v>12.9</v>
+      </c>
+      <c r="G744" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H744" s="1">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="745" customHeight="1" spans="1:8">
+      <c r="A745" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B745" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C745" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D745" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E745" s="1">
+        <v>125.6</v>
+      </c>
+      <c r="F745" s="1">
+        <v>12.6</v>
+      </c>
+      <c r="G745" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H745" s="1">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="746" customHeight="1" spans="1:8">
+      <c r="A746" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B746" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C746" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D746" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E746" s="1">
+        <v>125.7</v>
+      </c>
+      <c r="F746" s="1">
+        <v>12.3</v>
+      </c>
+      <c r="G746" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H746" s="1">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="747" customHeight="1" spans="1:8">
+      <c r="A747" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B747" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C747" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D747" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E747" s="1">
+        <v>103.2</v>
+      </c>
+      <c r="F747" s="1">
+        <v>11.8</v>
+      </c>
+      <c r="G747" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H747" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="748" customHeight="1" spans="1:8">
+      <c r="A748" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B748" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C748" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D748" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E748" s="1">
+        <v>102.6</v>
+      </c>
+      <c r="F748" s="1">
+        <v>11.2</v>
+      </c>
+      <c r="G748" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H748" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="749" customHeight="1" spans="1:8">
+      <c r="A749" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B749" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C749" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D749" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E749" s="1">
+        <v>102.1</v>
+      </c>
+      <c r="F749" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="G749" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H749" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="750" customHeight="1" spans="1:8">
+      <c r="A750" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B750" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C750" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D750" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E750" s="1">
+        <v>110.6</v>
+      </c>
+      <c r="F750" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="G750" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H750" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="751" customHeight="1" spans="1:8">
+      <c r="A751" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B751" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C751" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D751" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E751" s="1">
+        <v>131.7</v>
+      </c>
+      <c r="F751" s="1">
+        <v>10.4</v>
+      </c>
+      <c r="G751" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H751" s="1">
+        <v>9.3</v>
+      </c>
+    </row>
+    <row r="752" customHeight="1" spans="1:8">
+      <c r="A752" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B752" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C752" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D752" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E752" s="1">
+        <v>147.7</v>
+      </c>
+      <c r="F752" s="1">
+        <v>9.2</v>
+      </c>
+      <c r="G752" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H752" s="1">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="753" customHeight="1" spans="1:8">
+      <c r="A753" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B753" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C753" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D753" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E753" s="1">
+        <v>132.8</v>
+      </c>
+      <c r="F753" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G753" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H753" s="1">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="754" customHeight="1" spans="1:8">
+      <c r="A754" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B754" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C754" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D754" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E754" s="1">
+        <v>136.2</v>
+      </c>
+      <c r="F754" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G754" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H754" s="1">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="755" customHeight="1" spans="1:8">
+      <c r="A755" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B755" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C755" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D755" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E755" s="1">
+        <v>163.2</v>
+      </c>
+      <c r="F755" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="G755" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H755" s="1">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="756" customHeight="1" spans="1:8">
+      <c r="A756" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B756" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C756" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D756" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E756" s="1">
+        <v>140.8</v>
+      </c>
+      <c r="F756" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G756" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H756" s="1">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="757" customHeight="1" spans="1:8">
+      <c r="A757" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B757" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C757" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D757" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E757" s="1">
+        <v>149.5</v>
+      </c>
+      <c r="F757" s="1">
+        <v>4.4</v>
+      </c>
+      <c r="G757" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H757" s="1">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="758" customHeight="1" spans="1:8">
+      <c r="A758" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B758" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C758" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D758" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E758" s="1">
+        <v>159</v>
+      </c>
+      <c r="F758" s="1">
+        <v>2.3</v>
+      </c>
+      <c r="G758" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H758" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="759" customHeight="1" spans="1:8">
+      <c r="A759" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B759" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C759" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D759" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E759" s="1">
+        <v>133.4</v>
+      </c>
+      <c r="F759" s="1">
+        <v>-0.9</v>
+      </c>
+      <c r="G759" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H759" s="1">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="760" customHeight="1" spans="1:8">
+      <c r="A760" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B760" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C760" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D760" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E760" s="1">
+        <v>144.5</v>
+      </c>
+      <c r="F760" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G760" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="H760" s="1">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="761" customHeight="1" spans="1:8">
+      <c r="A761" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C761" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D761" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E761" s="1">
+        <v>140.2</v>
+      </c>
+      <c r="F761" s="1">
+        <v>58.5</v>
+      </c>
+      <c r="G761" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H761" s="1">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="762" customHeight="1" spans="1:8">
+      <c r="A762" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C762" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D762" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E762" s="1">
+        <v>107.2</v>
+      </c>
+      <c r="F762" s="1">
+        <v>21.2</v>
+      </c>
+      <c r="G762" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H762" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="763" customHeight="1" spans="1:8">
+      <c r="A763" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C763" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D763" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E763" s="1">
+        <v>104.5</v>
+      </c>
+      <c r="F763" s="1">
+        <v>19.3</v>
+      </c>
+      <c r="G763" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H763" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="764" customHeight="1" spans="1:8">
+      <c r="A764" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C764" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D764" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E764" s="1">
+        <v>116.8</v>
+      </c>
+      <c r="F764" s="1">
+        <v>16.8</v>
+      </c>
+      <c r="G764" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H764" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="765" customHeight="1" spans="1:8">
+      <c r="A765" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B765" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C765" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D765" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E765" s="1">
+        <v>194.7</v>
+      </c>
+      <c r="F765" s="1">
+        <v>16.6</v>
+      </c>
+      <c r="G765" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H765" s="1">
+        <v>61.8</v>
+      </c>
+    </row>
+    <row r="766" customHeight="1" spans="1:8">
+      <c r="A766" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B766" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C766" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D766" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E766" s="1">
+        <v>141.7</v>
+      </c>
+      <c r="F766" s="1">
+        <v>15.1</v>
+      </c>
+      <c r="G766" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H766" s="1">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="767" customHeight="1" spans="1:8">
+      <c r="A767" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C767" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D767" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E767" s="1">
+        <v>83.1</v>
+      </c>
+      <c r="F767" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="G767" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H767" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="768" customHeight="1" spans="1:8">
+      <c r="A768" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C768" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D768" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E768" s="1">
+        <v>136.9</v>
+      </c>
+      <c r="F768" s="1">
+        <v>13.2</v>
+      </c>
+      <c r="G768" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H768" s="1">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="769" customHeight="1" spans="1:8">
+      <c r="A769" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C769" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D769" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E769" s="1">
+        <v>125.9</v>
+      </c>
+      <c r="F769" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="G769" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H769" s="1">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="770" customHeight="1" spans="1:8">
+      <c r="A770" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C770" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D770" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E770" s="1">
+        <v>117</v>
+      </c>
+      <c r="F770" s="1">
+        <v>12.7</v>
+      </c>
+      <c r="G770" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H770" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="771" customHeight="1" spans="1:8">
+      <c r="A771" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B771" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C771" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D771" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E771" s="1">
+        <v>125.7</v>
+      </c>
+      <c r="F771" s="1">
+        <v>12.3</v>
+      </c>
+      <c r="G771" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H771" s="1">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="772" customHeight="1" spans="1:8">
+      <c r="A772" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C772" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D772" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E772" s="1">
+        <v>145.2</v>
+      </c>
+      <c r="F772" s="1">
+        <v>12.3</v>
+      </c>
+      <c r="G772" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H772" s="1">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="773" customHeight="1" spans="1:8">
+      <c r="A773" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B773" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C773" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D773" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E773" s="1">
+        <v>103.7</v>
+      </c>
+      <c r="F773" s="1">
+        <v>12.3</v>
+      </c>
+      <c r="G773" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H773" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="774" customHeight="1" spans="1:8">
+      <c r="A774" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B774" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C774" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D774" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E774" s="1">
+        <v>103.4</v>
+      </c>
+      <c r="F774" s="1">
+        <v>12</v>
+      </c>
+      <c r="G774" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H774" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="775" customHeight="1" spans="1:8">
+      <c r="A775" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B775" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C775" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D775" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E775" s="1">
+        <v>110.6</v>
+      </c>
+      <c r="F775" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="G775" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H775" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="776" customHeight="1" spans="1:8">
+      <c r="A776" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C776" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D776" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E776" s="1">
+        <v>102</v>
+      </c>
+      <c r="F776" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="G776" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H776" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="777" customHeight="1" spans="1:8">
+      <c r="A777" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C777" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D777" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E777" s="1">
+        <v>131.3</v>
+      </c>
+      <c r="F777" s="1">
+        <v>10.1</v>
+      </c>
+      <c r="G777" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H777" s="1">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="778" customHeight="1" spans="1:8">
+      <c r="A778" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C778" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D778" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E778" s="1">
+        <v>148.1</v>
+      </c>
+      <c r="F778" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="G778" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H778" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="779" customHeight="1" spans="1:8">
+      <c r="A779" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C779" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D779" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E779" s="1">
+        <v>132.7</v>
+      </c>
+      <c r="F779" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="G779" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H779" s="1">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="780" customHeight="1" spans="1:8">
+      <c r="A780" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B780" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C780" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D780" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E780" s="1">
+        <v>163.7</v>
+      </c>
+      <c r="F780" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="G780" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H780" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="781" customHeight="1" spans="1:8">
+      <c r="A781" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B781" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C781" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D781" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E781" s="1">
+        <v>136</v>
+      </c>
+      <c r="F781" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G781" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H781" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="782" customHeight="1" spans="1:8">
+      <c r="A782" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C782" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D782" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E782" s="1">
+        <v>140.6</v>
+      </c>
+      <c r="F782" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="G782" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H782" s="1">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="783" customHeight="1" spans="1:8">
+      <c r="A783" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B783" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C783" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D783" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E783" s="1">
+        <v>149.2</v>
+      </c>
+      <c r="F783" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="G783" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H783" s="1">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="784" customHeight="1" spans="1:8">
+      <c r="A784" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B784" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C784" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D784" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E784" s="1">
+        <v>159</v>
+      </c>
+      <c r="F784" s="1">
+        <v>2.2</v>
+      </c>
+      <c r="G784" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H784" s="1">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="785" customHeight="1" spans="1:8">
+      <c r="A785" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B785" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C785" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D785" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E785" s="1">
+        <v>133.9</v>
+      </c>
+      <c r="F785" s="1">
+        <v>-0.5</v>
+      </c>
+      <c r="G785" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H785" s="1">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="786" customHeight="1" spans="1:8">
+      <c r="A786" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B786" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C786" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D786" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E786" s="1">
+        <v>143.9</v>
+      </c>
+      <c r="F786" s="1">
+        <v>-1.5</v>
+      </c>
+      <c r="G786" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="H786" s="1">
+        <v>19.5</v>
       </c>
     </row>
   </sheetData>
